--- a/data/trans_dic/P3A_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,73</t>
+          <t>1,35; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,02</t>
+          <t>3,18; 5,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,2</t>
+          <t>1,11; 3,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,21</t>
+          <t>4,83; 8,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,23</t>
+          <t>1,06; 3,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,81</t>
+          <t>2,64; 5,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,49</t>
+          <t>1,61; 4,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,88</t>
+          <t>4,99; 7,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,95</t>
+          <t>1,48; 2,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,39</t>
+          <t>3,17; 5,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,47</t>
+          <t>1,62; 3,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,53</t>
+          <t>5,37; 7,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,15</t>
+          <t>2,53; 5,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,64</t>
+          <t>3,0; 5,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,25</t>
+          <t>1,34; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,47</t>
+          <t>1,46; 4,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,62</t>
+          <t>0,92; 2,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,53</t>
+          <t>2,87; 5,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,7</t>
+          <t>1,53; 3,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,39</t>
+          <t>4,13; 6,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,48</t>
+          <t>1,92; 3,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,1</t>
+          <t>3,18; 5,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,1</t>
+          <t>1,68; 3,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,97</t>
+          <t>2,65; 4,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,34</t>
+          <t>2,33; 5,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,56</t>
+          <t>1,18; 3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,8</t>
+          <t>1,32; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,5</t>
+          <t>2,53; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,07</t>
+          <t>2,05; 5,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,37</t>
+          <t>2,33; 5,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,95</t>
+          <t>1,45; 3,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,44</t>
+          <t>1,61; 5,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,6</t>
+          <t>2,63; 4,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,1</t>
+          <t>2,1; 4,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,32</t>
+          <t>1,6; 3,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,84</t>
+          <t>2,44; 4,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,87</t>
+          <t>4,62; 7,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,92</t>
+          <t>3,18; 5,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,52</t>
+          <t>2,27; 4,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,74</t>
+          <t>3,86; 6,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,64</t>
+          <t>3,88; 6,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,79</t>
+          <t>4,64; 7,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,59</t>
+          <t>2,95; 5,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,43</t>
+          <t>4,74; 7,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,61</t>
+          <t>4,69; 6,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,26</t>
+          <t>4,4; 6,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,61</t>
+          <t>2,76; 4,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,6</t>
+          <t>4,73; 6,67</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,77</t>
+          <t>3,4; 4,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,51</t>
+          <t>3,13; 4,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,01</t>
+          <t>1,9; 2,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,19</t>
+          <t>3,34; 5,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,81</t>
+          <t>2,55; 3,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,42</t>
+          <t>3,81; 5,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,73</t>
+          <t>2,48; 3,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,02</t>
+          <t>4,23; 6,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,08</t>
+          <t>3,15; 4,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,69</t>
+          <t>3,75; 4,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,18</t>
+          <t>2,3; 3,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,45</t>
+          <t>4,18; 5,44</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9434; 25901</t>
+          <t>9346; 24266</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20779; 42378</t>
+          <t>22350; 41881</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7665; 21598</t>
+          <t>7483; 22225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30578; 52113</t>
+          <t>30660; 51967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7710; 22208</t>
+          <t>7293; 23074</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18454; 40515</t>
+          <t>18418; 40924</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11021; 30199</t>
+          <t>10814; 30739</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36343; 57186</t>
+          <t>36178; 57806</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20190; 40806</t>
+          <t>20414; 41362</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44385; 75453</t>
+          <t>44336; 74972</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22455; 46678</t>
+          <t>21835; 45881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73307; 102437</t>
+          <t>73002; 102025</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23808; 49566</t>
+          <t>24367; 48148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30240; 57342</t>
+          <t>30464; 58693</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13646; 33206</t>
+          <t>13722; 31673</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16462; 53347</t>
+          <t>17449; 53063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9352; 25410</t>
+          <t>8903; 25352</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29635; 57065</t>
+          <t>29601; 56847</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15972; 38591</t>
+          <t>15947; 40063</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40087; 61274</t>
+          <t>39628; 60914</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37827; 67106</t>
+          <t>36982; 67842</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65997; 104573</t>
+          <t>65218; 103831</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34383; 63957</t>
+          <t>34613; 63354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58873; 107001</t>
+          <t>57097; 104993</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16573; 36235</t>
+          <t>15804; 36673</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9163; 27006</t>
+          <t>8952; 28108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10344; 28698</t>
+          <t>9940; 28266</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18258; 38723</t>
+          <t>17834; 37817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14797; 34511</t>
+          <t>13976; 34185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17670; 41653</t>
+          <t>18048; 40626</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11657; 30935</t>
+          <t>11386; 30462</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17682; 50731</t>
+          <t>15039; 48412</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34815; 62556</t>
+          <t>35683; 63868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32376; 62876</t>
+          <t>32213; 62191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25837; 51083</t>
+          <t>24620; 52146</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40163; 79310</t>
+          <t>39897; 78267</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42795; 74042</t>
+          <t>43531; 72734</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30790; 56072</t>
+          <t>30177; 56242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20951; 42220</t>
+          <t>21177; 42704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35956; 62441</t>
+          <t>35787; 61263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40583; 68956</t>
+          <t>40296; 69758</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48880; 81909</t>
+          <t>48793; 80473</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30385; 58336</t>
+          <t>30739; 58407</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52277; 81205</t>
+          <t>51868; 81020</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91378; 130911</t>
+          <t>92831; 131844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84780; 125211</t>
+          <t>87928; 128177</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56650; 91174</t>
+          <t>54600; 92132</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95220; 133396</t>
+          <t>95519; 134694</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>110225; 156128</t>
+          <t>111528; 161196</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107733; 154617</t>
+          <t>107120; 156295</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66300; 101792</t>
+          <t>64369; 100996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115754; 179417</t>
+          <t>115599; 174998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>87566; 128710</t>
+          <t>86206; 126266</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>139713; 192863</t>
+          <t>135629; 188487</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84935; 132123</t>
+          <t>87941; 132776</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>165465; 223279</t>
+          <t>157053; 225152</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>211408; 271328</t>
+          <t>209386; 269777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>260008; 327290</t>
+          <t>261714; 328811</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162745; 220265</t>
+          <t>158996; 218791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>303718; 390597</t>
+          <t>299741; 389766</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,5</t>
+          <t>1,38; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,95</t>
+          <t>2,96; 5,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,29</t>
+          <t>1,1; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,18</t>
+          <t>4,64; 7,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,36</t>
+          <t>1,13; 3,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,87</t>
+          <t>2,78; 5,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,57</t>
+          <t>1,67; 4,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,97</t>
+          <t>5,71; 8,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,99</t>
+          <t>1,49; 3,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,35</t>
+          <t>3,22; 5,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,41</t>
+          <t>1,58; 3,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,5</t>
+          <t>5,58; 7,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,01</t>
+          <t>2,54; 5,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,77</t>
+          <t>3,03; 5,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,1</t>
+          <t>1,37; 3,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,45</t>
+          <t>2,62; 5,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,62</t>
+          <t>0,89; 2,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,51</t>
+          <t>2,95; 5,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,84</t>
+          <t>1,55; 3,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,35</t>
+          <t>4,12; 6,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,51</t>
+          <t>1,97; 3,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,07</t>
+          <t>3,32; 5,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,07</t>
+          <t>1,67; 3,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,88</t>
+          <t>3,65; 5,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,4</t>
+          <t>2,46; 5,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,71</t>
+          <t>1,17; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,74</t>
+          <t>1,33; 3,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,37</t>
+          <t>2,6; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,02</t>
+          <t>2,2; 4,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,24</t>
+          <t>2,53; 5,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,89</t>
+          <t>1,45; 3,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,19</t>
+          <t>3,81; 6,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,7</t>
+          <t>2,61; 4,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,06</t>
+          <t>2,13; 4,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,39</t>
+          <t>1,72; 3,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,78</t>
+          <t>3,62; 5,5</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,73</t>
+          <t>4,64; 7,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,93</t>
+          <t>3,14; 5,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,58</t>
+          <t>2,22; 4,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,61</t>
+          <t>3,76; 6,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,72</t>
+          <t>3,83; 6,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,65</t>
+          <t>4,59; 7,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,6</t>
+          <t>2,79; 5,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,41</t>
+          <t>5,43; 7,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,66</t>
+          <t>4,63; 6,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,41</t>
+          <t>4,23; 6,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,66</t>
+          <t>2,85; 4,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 6,67</t>
+          <t>4,93; 6,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,92</t>
+          <t>3,41; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,56</t>
+          <t>3,11; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,98</t>
+          <t>1,96; 2,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,06</t>
+          <t>3,94; 5,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,74</t>
+          <t>2,57; 3,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,3</t>
+          <t>3,81; 5,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,75</t>
+          <t>2,48; 3,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,07</t>
+          <t>5,22; 6,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,06</t>
+          <t>3,18; 4,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,71</t>
+          <t>3,68; 4,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,16</t>
+          <t>2,35; 3,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,44</t>
+          <t>4,77; 5,73</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47512</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87518</t>
+          <t>93525</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9346; 24266</t>
+          <t>9589; 24185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22350; 41881</t>
+          <t>20797; 41908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7483; 22225</t>
+          <t>7434; 21993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30660; 51967</t>
+          <t>32038; 54155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7293; 23074</t>
+          <t>7786; 22431</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18418; 40924</t>
+          <t>19353; 39764</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10814; 30739</t>
+          <t>11217; 30925</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36178; 57806</t>
+          <t>41939; 61272</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20414; 41362</t>
+          <t>20595; 41838</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44336; 74972</t>
+          <t>45036; 74547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21835; 45881</t>
+          <t>21290; 46270</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73002; 102025</t>
+          <t>79526; 109724</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35255</t>
+          <t>39594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84639</t>
+          <t>93643</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24367; 48148</t>
+          <t>24438; 48196</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30464; 58693</t>
+          <t>30780; 57973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13722; 31673</t>
+          <t>14025; 34953</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17449; 53063</t>
+          <t>27498; 58077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8903; 25352</t>
+          <t>8660; 25228</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29601; 56847</t>
+          <t>30468; 56907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15947; 40063</t>
+          <t>16190; 41299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39628; 60914</t>
+          <t>44185; 66405</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36982; 67842</t>
+          <t>37931; 67923</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65218; 103831</t>
+          <t>68090; 104239</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34613; 63354</t>
+          <t>34438; 64176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57097; 104993</t>
+          <t>77336; 113393</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26717</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35001</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>71591</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15804; 36673</t>
+          <t>16658; 35921</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8952; 28108</t>
+          <t>8853; 27124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9940; 28266</t>
+          <t>10014; 27737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17834; 37817</t>
+          <t>20904; 44580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13976; 34185</t>
+          <t>14978; 33928</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18048; 40626</t>
+          <t>19650; 42159</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11386; 30462</t>
+          <t>11326; 31164</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15039; 48412</t>
+          <t>30979; 51314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35683; 63868</t>
+          <t>35529; 63091</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32213; 62191</t>
+          <t>32576; 63526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24620; 52146</t>
+          <t>26389; 52621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39897; 78267</t>
+          <t>58472; 88880</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47072</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>113903</t>
+          <t>121018</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43531; 72734</t>
+          <t>43671; 74328</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30177; 56242</t>
+          <t>29750; 56112</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21177; 42704</t>
+          <t>20746; 41479</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35787; 61263</t>
+          <t>37243; 64833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40296; 69758</t>
+          <t>39806; 68999</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48793; 80473</t>
+          <t>48332; 83048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30739; 58407</t>
+          <t>29053; 57255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51868; 81020</t>
+          <t>60731; 86906</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92831; 131844</t>
+          <t>91603; 131904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87928; 128177</t>
+          <t>84659; 125525</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54600; 92132</t>
+          <t>56356; 93285</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95519; 134694</t>
+          <t>103820; 141122</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149050</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>218358</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>347779</t>
+          <t>379778</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>111528; 161196</t>
+          <t>111755; 157176</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107120; 156295</t>
+          <t>106620; 154326</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64369; 100996</t>
+          <t>66300; 100802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115599; 174998</t>
+          <t>139060; 189508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>86206; 126266</t>
+          <t>86834; 128260</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>135629; 188487</t>
+          <t>135337; 187871</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87941; 132776</t>
+          <t>87896; 132928</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>157053; 225152</t>
+          <t>195052; 241052</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>209386; 269777</t>
+          <t>211271; 270028</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>261714; 328811</t>
+          <t>256649; 329203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158996; 218791</t>
+          <t>162606; 221779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>299741; 389766</t>
+          <t>346329; 416088</t>
         </is>
       </c>
     </row>
